--- a/datasets/IT and RD.kz.xlsx
+++ b/datasets/IT and RD.kz.xlsx
@@ -15,6 +15,9 @@
     <sheet name="ITcosts" sheetId="1" r:id="rId1"/>
     <sheet name="RDcosts" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -671,7 +674,533 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>РФ, млн. руб. (с учётом инфляции)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]ITcosts!$A$102</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Затраты на IT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[1]ITcosts!$B$101:$K$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]ITcosts!$B$102:$K$102</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1249224.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1450150.0098000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1562349.8545200001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2088855.2804</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2107890.2212499999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2702234.0419200002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2429034.2678999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2328987.3884000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2517145.44</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2535488.6239999989</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CE65-4B87-BC99-0C1A186A68E7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]ITcosts!$A$103</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Затраты на НИОКР</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[1]ITcosts!$B$101:$K$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]ITcosts!$B$103:$K$103</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1258011.3489000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1322069.9945690399</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1301112.5709929101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1320159.82832328</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1322003.429241</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1274990.10925734</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1166052.98225308</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1187485.25751488</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1127081.4147359999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1072341.0380855999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CE65-4B87-BC99-0C1A186A68E7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="132847776"/>
+        <c:axId val="132852352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="132847776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="132852352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="132852352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="132847776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1227,6 +1756,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1259,7 +2304,157 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>176213</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="ITcosts"/>
+      <sheetName val="RDcosts"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="101">
+          <cell r="B101">
+            <v>2016</v>
+          </cell>
+          <cell r="C101">
+            <v>2017</v>
+          </cell>
+          <cell r="D101">
+            <v>2018</v>
+          </cell>
+          <cell r="E101">
+            <v>2019</v>
+          </cell>
+          <cell r="F101">
+            <v>2020</v>
+          </cell>
+          <cell r="G101">
+            <v>2021</v>
+          </cell>
+          <cell r="H101">
+            <v>2022</v>
+          </cell>
+          <cell r="I101">
+            <v>2023</v>
+          </cell>
+          <cell r="J101">
+            <v>2024</v>
+          </cell>
+          <cell r="K101">
+            <v>2025</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102" t="str">
+            <v>Затраты на IT</v>
+          </cell>
+          <cell r="B102">
+            <v>1249224.8</v>
+          </cell>
+          <cell r="C102">
+            <v>1450150.0098000001</v>
+          </cell>
+          <cell r="D102">
+            <v>1562349.8545200001</v>
+          </cell>
+          <cell r="E102">
+            <v>2088855.2804</v>
+          </cell>
+          <cell r="F102">
+            <v>2107890.2212499999</v>
+          </cell>
+          <cell r="G102">
+            <v>2702234.0419200002</v>
+          </cell>
+          <cell r="H102">
+            <v>2429034.2678999999</v>
+          </cell>
+          <cell r="I102">
+            <v>2328987.3884000001</v>
+          </cell>
+          <cell r="J102">
+            <v>2517145.44</v>
+          </cell>
+          <cell r="K102">
+            <v>2535488.6239999989</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>Затраты на НИОКР</v>
+          </cell>
+          <cell r="B103">
+            <v>1258011.3489000001</v>
+          </cell>
+          <cell r="C103">
+            <v>1322069.9945690399</v>
+          </cell>
+          <cell r="D103">
+            <v>1301112.5709929101</v>
+          </cell>
+          <cell r="E103">
+            <v>1320159.82832328</v>
+          </cell>
+          <cell r="F103">
+            <v>1322003.429241</v>
+          </cell>
+          <cell r="G103">
+            <v>1274990.10925734</v>
+          </cell>
+          <cell r="H103">
+            <v>1166052.98225308</v>
+          </cell>
+          <cell r="I103">
+            <v>1187485.25751488</v>
+          </cell>
+          <cell r="J103">
+            <v>1127081.4147359999</v>
+          </cell>
+          <cell r="K103">
+            <v>1072341.0380855999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
